--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
@@ -39,60 +39,60 @@
     <t xml:space="preserve">Chillán Viejo</t>
   </si>
   <si>
+    <t xml:space="preserve">San Nicolás</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Fabián</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quillón</t>
   </si>
   <si>
+    <t xml:space="preserve">Bulnes</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Carlos</t>
   </si>
   <si>
-    <t xml:space="preserve">San Nicolás</t>
-  </si>
-  <si>
     <t xml:space="preserve">Coihueco</t>
   </si>
   <si>
     <t xml:space="preserve">Pinto</t>
   </si>
   <si>
+    <t xml:space="preserve">Portezuelo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">San Fabián</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulnes</t>
-  </si>
-  <si>
     <t xml:space="preserve">El Carmen</t>
   </si>
   <si>
+    <t xml:space="preserve">Ranquil</t>
+  </si>
+  <si>
     <t xml:space="preserve">Coelemu</t>
   </si>
   <si>
+    <t xml:space="preserve">Quirihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Ignacio</t>
   </si>
   <si>
-    <t xml:space="preserve">Portezuelo</t>
+    <t xml:space="preserve">Ninhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treguaco</t>
   </si>
   <si>
     <t xml:space="preserve">Cobquecura</t>
   </si>
   <si>
-    <t xml:space="preserve">Quirihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pemuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranquil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treguaco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ñiquén</t>
   </si>
   <si>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:47</t>
+    <t xml:space="preserve">2026-09-24 00:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -538,7 +538,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>3471</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="3">
@@ -549,13 +549,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>16107</v>
+        <v>16305</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2812</v>
+        <v>865</v>
       </c>
     </row>
     <row r="4">
@@ -566,13 +566,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>16301</v>
+        <v>16304</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2640</v>
+        <v>818</v>
       </c>
     </row>
     <row r="5">
@@ -583,13 +583,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>16305</v>
+        <v>16107</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2517</v>
+        <v>759</v>
       </c>
     </row>
     <row r="6">
@@ -600,13 +600,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>16302</v>
+        <v>16102</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2145</v>
+        <v>656</v>
       </c>
     </row>
     <row r="7">
@@ -617,13 +617,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>16106</v>
+        <v>16301</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1996</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -634,13 +634,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>16109</v>
+        <v>16302</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1525</v>
+        <v>646</v>
       </c>
     </row>
     <row r="9">
@@ -651,13 +651,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>16304</v>
+        <v>16106</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10">
@@ -668,13 +668,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>16102</v>
+        <v>16205</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1446</v>
+        <v>424</v>
       </c>
     </row>
     <row r="11">
@@ -685,13 +685,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>16104</v>
+        <v>16109</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1209</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12">
@@ -702,13 +702,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>16203</v>
+        <v>16104</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>971</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13">
@@ -719,13 +719,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>16108</v>
+        <v>16206</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>847</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14">
@@ -736,13 +736,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>16205</v>
+        <v>16203</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>781</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -753,13 +753,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>16202</v>
+        <v>16201</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>553</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16">
@@ -770,13 +770,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>16201</v>
+        <v>16105</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>525</v>
+        <v>97</v>
       </c>
     </row>
     <row r="17">
@@ -787,13 +787,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>16105</v>
+        <v>16108</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>522</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -810,7 +810,7 @@
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>394</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -821,13 +821,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>16206</v>
+        <v>16207</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>378</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -838,13 +838,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>16207</v>
+        <v>16202</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-177</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -861,7 +861,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-1730</v>
+        <v>-147</v>
       </c>
     </row>
     <row r="22">
@@ -878,7 +878,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-2185</v>
+        <v>-1841</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:25</t>
+    <t xml:space="preserve">2026-09-27 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:14</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">El Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Coelemu</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:25</t>
+    <t xml:space="preserve">2026-10-04 08:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:09</t>
+    <t xml:space="preserve">2026-10-05 08:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
